--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="159">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Serie imagerie</t>
+    <t>Logical model - FR LM Serie imagerie</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:27:00+00:00</t>
+    <t>2026-04-24T08:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,44 +250,223 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-serie-imagerie.uuidSerie</t>
+    <t>fr-lm-serie-imagerie.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>UUID serie</t>
-  </si>
-  <si>
-    <t>fr-lm-serie-imagerie.code</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.participant[x]</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.uuidSerie</t>
+  </si>
+  <si>
+    <t>UUID serie</t>
+  </si>
+  <si>
+    <t>fr-lm-serie-imagerie.code</t>
+  </si>
+  <si>
     <t>Code de l'entrée</t>
   </si>
   <si>
-    <t>fr-lm-serie-imagerie.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l'entrée</t>
-  </si>
-  <si>
     <t>fr-lm-serie-imagerie.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>Date de la série d'actes</t>
@@ -304,10 +483,6 @@
   </si>
   <si>
     <t>fr-lm-serie-imagerie.referenceWado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
   </si>
   <si>
     <t>Référence WADO</t>
@@ -631,11 +806,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="52.875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -644,7 +819,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.77734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -658,14 +833,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -897,7 +1072,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>73</v>
@@ -966,13 +1141,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -983,10 +1158,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1009,13 +1184,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1066,7 +1241,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1083,10 +1258,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1097,7 +1272,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1109,13 +1284,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1166,13 +1341,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1183,10 +1358,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1197,7 +1372,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1209,13 +1384,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1266,13 +1441,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1283,10 +1458,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1294,10 +1469,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1309,13 +1484,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1366,13 +1541,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1383,10 +1558,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1394,10 +1569,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1409,13 +1584,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1466,13 +1641,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1483,10 +1658,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1494,10 +1669,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1509,13 +1684,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1566,13 +1741,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1583,10 +1758,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1594,10 +1769,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1609,13 +1784,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1666,13 +1841,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1683,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1694,10 +1869,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1709,13 +1884,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1766,18 +1941,1618 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-serie-imagerie.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-serie-imagerie.header.langue</t>
+    <t>fr-lm-serie-imagerie.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-serie-imagerie.uuidSerie</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -833,8 +827,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2469,7 +2463,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2520,31 +2514,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2558,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2587,10 +2581,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2641,7 +2635,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2658,10 +2652,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2687,10 +2681,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2741,7 +2735,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2758,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2787,10 +2781,10 @@
         <v>88</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2841,7 +2835,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2858,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2887,10 +2881,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2941,7 +2935,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2958,10 +2952,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2987,10 +2981,10 @@
         <v>127</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3041,7 +3035,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3058,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3084,13 +3078,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3141,7 +3135,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3158,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3187,10 +3181,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3241,7 +3235,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3258,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3287,10 +3281,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3341,7 +3335,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3358,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3387,10 +3381,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3441,7 +3435,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3458,10 +3452,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3484,13 +3478,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3541,7 +3535,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-serie-imagerie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
